--- a/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
+++ b/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
@@ -1655,7 +1655,7 @@
       <c r="F53" s="13" t="n"/>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>WHEN A FREE SPIN HAS BOTH A REGULAR-SYMBOL WIN AND [C2] / [C3] ON THE FINAL REELS, THE SUM OF THOSE VALUES IS ADDED TO THE CARRYING MULTIPLIER.</t>
+          <t>WHEN A FREE SPIN HAS BOTH A REGULAR-SYMBOL WIN AND [C2] / [C3] ON THE FINAL REELS, THE SUM OF THOSE VALUES IS ADDED TO THE ACCUMULATED MULTIPLIER.</t>
         </is>
       </c>
       <c r="H53" s="12" t="n"/>
@@ -1673,7 +1673,7 @@
       <c r="F54" s="13" t="n"/>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>FREE SPINS WITH ONLY A [C1] WIN, OR WITH NO WIN, DO NOT ADD TO THE CARRYING MULTIPLIER.</t>
+          <t>FREE SPINS WITH ONLY A [C1] WIN, OR WITH NO WIN, DO NOT ADD TO THE ACCUMULATED MULTIPLIER.</t>
         </is>
       </c>
       <c r="H54" s="12" t="n"/>
@@ -1691,7 +1691,7 @@
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>THE CARRYING MULTIPLIER APPLIES ONLY ON A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1}X AND THE CARRYING MULTIPLIER IS KEPT, NOT RESET.</t>
+          <t>THE ACCUMULATED MULTIPLIER APPLIES ONLY ON A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1}X AND THE ACCUMULATED MULTIPLIER IS KEPT, NOT RESET.</t>
         </is>
       </c>
       <c r="H55" s="12" t="n"/>
@@ -1727,7 +1727,7 @@
       <c r="F57" s="13" t="n"/>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>THE CARRYING MULTIPLIER IS KEPT UNTIL THE FREE GAME FEATURE ENDS.</t>
+          <t>THE ACCUMULATED MULTIPLIER IS KEPT UNTIL THE FREE GAME FEATURE ENDS.</t>
         </is>
       </c>
       <c r="H57" s="12" t="n"/>

--- a/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
+++ b/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
@@ -723,14 +723,14 @@
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>{4}／{5}／{6} 个 [C1] 分别支付 {3}／{5}／{100} × 投注。{3} 个 [C1] 不支付奖金。</t>
+          <t>{4}／{5}／{6} 个 [C1] 分别支付 {3X}／{5X}／{100X} 投注。{3} 个 [C1] 不支付奖金。</t>
         </is>
       </c>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>{4} / {5} / {6} [C1] PAY {3} / {5} / {100} × BET RESPECTIVELY. {3} [C1] DO NOT PAY.</t>
+          <t>{4} / {5} / {6} [C1] PAY {3X} / {5X} / {100X} BET RESPECTIVELY. {3} [C1] DO NOT PAY.</t>
         </is>
       </c>
       <c r="H11" s="12" t="n"/>
@@ -829,14 +829,14 @@
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>[C3] 于每次中奖消除后提升一个倍数等级，单颗最高为 {2500}x。</t>
+          <t>[C3] 于每次中奖消除后提升一个倍数等级，单颗最高为 {2500X}。</t>
         </is>
       </c>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>[C3] IS UPGRADED BY ONE LEVEL AFTER EACH WINNING CASCADE, UP TO {2500}X PER SYMBOL.</t>
+          <t>[C3] IS UPGRADED BY ONE LEVEL AFTER EACH WINNING CASCADE, UP TO {2500X} PER SYMBOL.</t>
         </is>
       </c>
       <c r="H16" s="12" t="n"/>
@@ -872,7 +872,7 @@
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>WHEN SEVERAL [C2]／[C3] APPEAR ON THE SAME FINAL REELS, THEIR VALUES ARE ADDED TOGETHER.</t>
+          <t>WHEN SEVERAL [C2] / [C3] APPEAR ON THE SAME FINAL REELS, THEIR VALUES ARE ADDED TOGETHER.</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
@@ -1490,7 +1490,7 @@
       <c r="F44" s="13" t="n"/>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>IN THE FREE GAME FEATURE THE MULTIPLIERS ACCUMULATE.</t>
+          <t>IN THE FREE GAME FEATURE, THE MULTIPLIERS ACCUMULATE.</t>
         </is>
       </c>
       <c r="H44" s="12" t="n"/>
@@ -1619,7 +1619,7 @@
       <c r="F51" s="13" t="n"/>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>DURING FREE GAME, {3} OR MORE [C1] WILL RETRIGGER ADDITIONAL {5} FREE SPINS.</t>
+          <t>DURING THE FREE GAME FEATURE, {3} OR MORE [C1] AWARD {5} ADDITIONAL FREE SPINS.</t>
         </is>
       </c>
       <c r="H51" s="12" t="n"/>
@@ -1684,14 +1684,14 @@
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>累积倍数只在“该次最终盘面本身有 [C2]／[C3]”时作用。有一般符号得奖但盘面没有倍数符号时，该次以 {1}x 结算，累积倍数保留不归零。</t>
+          <t>累积倍数只在“该次最终盘面本身有 [C2]／[C3]”时作用。有一般符号得奖但盘面没有倍数符号时，该次以 {1X} 结算，累积倍数保留不归零。</t>
         </is>
       </c>
       <c r="E55" s="12" t="n"/>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>THE ACCUMULATED MULTIPLIER APPLIES ONLY ON A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1}X AND THE ACCUMULATED MULTIPLIER IS KEPT, NOT RESET.</t>
+          <t>THE ACCUMULATED MULTIPLIER APPLIES ONLY TO A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1X} AND THE ACCUMULATED MULTIPLIER IS KEPT, NOT RESET.</t>
         </is>
       </c>
       <c r="H55" s="12" t="n"/>
@@ -1813,14 +1813,14 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>额外投注的扣款为 {2} × 您所选的基础投注。</t>
+          <t>额外投注的扣款为您所选基础投注的 {2X}。</t>
         </is>
       </c>
       <c r="E62" s="12" t="n"/>
       <c r="F62" s="13" t="n"/>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>EXTRA BET COSTS {2} × THE BASE BET YOU SELECT.</t>
+          <t>EXTRA BET COSTS {2X} THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H62" s="12" t="n"/>
@@ -1942,14 +1942,14 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>玩家可支付 {100}x 总投注，直接购买一次免费游戏进场机会。</t>
+          <t>玩家可支付 {100X} 总投注，直接购买一次免费游戏进场机会。</t>
         </is>
       </c>
       <c r="E69" s="12" t="n"/>
       <c r="F69" s="13" t="n"/>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>BUY FEATURE CAN BE PURCHASED FOR {100}X TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>BUY FEATURE CAN BE PURCHASED FOR {100X} THE TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H69" s="12" t="n"/>
@@ -1978,14 +1978,14 @@
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>进场盘面的 {4} 个 [C1] 依赔率表支付 {3} × 投注。</t>
+          <t>进场盘面的 {4} 个 [C1] 依赔率表支付 {3X} 投注。</t>
         </is>
       </c>
       <c r="E71" s="12" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>THE {4} [C1] ON THE ENTRY REELS PAY {3} × BET ACCORDING TO THE PAYTABLE.</t>
+          <t>THE {4} [C1] ON THE ENTRY REELS PAY {3X} BET ACCORDING TO THE PAYTABLE.</t>
         </is>
       </c>
       <c r="H71" s="12" t="n"/>
@@ -2114,7 +2114,7 @@
       <c r="F78" s="13" t="n"/>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>THE OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H78" s="12" t="n"/>
@@ -2132,7 +2132,7 @@
       <c r="F79" s="13" t="n"/>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>DURING OP JACKPOT FEATURE, THERE ARE {12} [COIN] WHICH CONSIST OF [GRAND], [MAJOR], [MINOR], AND [MINI].</t>
+          <t>DURING THE OP JACKPOT FEATURE, THERE ARE {12} [COIN], WHICH CONSIST OF [GRAND], [MAJOR], [MINOR], AND [MINI].</t>
         </is>
       </c>
       <c r="H79" s="12" t="n"/>
@@ -2168,7 +2168,7 @@
       <c r="F81" s="13" t="n"/>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>IF PLAYER GETS {3} SAME JACKPOT SYMBOLS WILL WIN THE JACKPOT AND CALCULATE THE TOTAL WIN.</t>
+          <t>IF THE PLAYER REVEALS {3} OF THE SAME JACKPOT SYMBOL, THE PLAYER WINS THAT JACKPOT AND IT IS ADDED TO THE TOTAL WIN.</t>
         </is>
       </c>
       <c r="H81" s="12" t="n"/>
@@ -2186,7 +2186,7 @@
       <c r="F82" s="13" t="n"/>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>[GRAND] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [GRAND] WILL BE UNLOCKED.</t>
+          <t>[GRAND] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [GRAND] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H82" s="12" t="n"/>
@@ -2204,7 +2204,7 @@
       <c r="F83" s="13" t="n"/>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>[MAJOR] IS LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [MAJOR] WILL BE UNLOCKED.</t>
+          <t>[MAJOR] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [MAJOR] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H83" s="12" t="n"/>
@@ -2222,7 +2222,7 @@
       <c r="F84" s="13" t="n"/>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H84" s="12" t="n"/>
@@ -2240,7 +2240,7 @@
       <c r="F85" s="13" t="n"/>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS DIFFERENT BET OPTION.</t>
+          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H85" s="12" t="n"/>
@@ -2258,7 +2258,7 @@
       <c r="F86" s="13" t="n"/>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>THE HIGHER BET, THE HIGHER CHANCES TO TRIGGER OP JACKPOT FEATURE.</t>
+          <t>THE HIGHER THE BET, THE HIGHER THE CHANCE TO TRIGGER THE OP JACKPOT FEATURE.</t>
         </is>
       </c>
       <c r="H86" s="12" t="n"/>
@@ -2380,14 +2380,14 @@
       <c r="C93" s="10" t="n"/>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>一般符号奖金为“赔率 × 投注”。</t>
+          <t>一般符号奖金依赔率表倍数乘以投注计算。</t>
         </is>
       </c>
       <c r="E93" s="12" t="n"/>
       <c r="F93" s="13" t="n"/>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>A REGULAR SYMBOL WIN IS CALCULATED AS THE PAYTABLE VALUE × BET.</t>
+          <t>A REGULAR SYMBOL WIN IS PAID AT THE PAYTABLE MULTIPLIER OF THE BET.</t>
         </is>
       </c>
       <c r="H93" s="12" t="n"/>
@@ -2498,7 +2498,7 @@
       <c r="F99" s="13" t="n"/>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>SELECT BET OPTION YOU WISH TO PLAY.</t>
+          <t>SELECT THE BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
       <c r="H99" s="12" t="n"/>
@@ -2516,7 +2516,7 @@
       <c r="F100" s="13" t="n"/>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>ALL WINS ARE MULTIPLIED BY BET OPTION EXCEPT PROGRESSIVES BONUSES.</t>
+          <t>ALL WINS ARE MULTIPLIED BY THE BET OPTION EXCEPT PROGRESSIVE BONUSES.</t>
         </is>
       </c>
       <c r="H100" s="12" t="n"/>

--- a/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
+++ b/Slots/H027_宙斯 2500/文件/101027_Help.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15.75" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -723,14 +722,14 @@
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>{4}／{5}／{6} 个 [C1] 分别支付 {3X}／{5X}／{100X} 投注。{3} 个 [C1] 不支付奖金。</t>
+          <t>{4}／{5}／{6} 个 [C1] 分别支付 {3}X／{5}X／{100}X 投注。{3} 个 [C1] 不支付奖金。</t>
         </is>
       </c>
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>{4} / {5} / {6} [C1] PAY {3X} / {5X} / {100X} BET RESPECTIVELY. {3} [C1] DO NOT PAY.</t>
+          <t>{4} / {5} / {6} [C1] PAY {3}X / {5}X / {100}X BET RESPECTIVELY. {3} [C1] DO NOT PAY.</t>
         </is>
       </c>
       <c r="H11" s="12" t="n"/>
@@ -806,99 +805,91 @@
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="13" t="n"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="63" customHeight="1">
       <c r="B15" s="10" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>[C2] 出现时即固定其倍数，之后不再改变。</t>
+          <t>[C2] 或 [C3] 出现时会带有随机倍数，可能的倍数包括 {2}X、{3}X、{4}X、{5}X、{6}X、{8}X、{10}X、{12}X、{15}X、{20}X、{25}X、{50}X、{100}X、{250}X、{500}X、{1000}X 或 {2500}X。</t>
         </is>
       </c>
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="13" t="n"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>[C2] KEEPS THE VALUE IT APPEARS WITH.</t>
+          <t>WHEN [C2] OR [C3] APPEARS, A RANDOM MULTIPLIER WILL BE APPLIED, INCLUDING VALUES SUCH AS {2}X, {3}X, {4}X, {5}X, {6}X, {8}X, {10}X, {12}X, {15}X, {20}X, {25}X, {50}X, {100}X, {250}X, {500}X, {1000}X OR {2500}X.</t>
         </is>
       </c>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="13" t="n"/>
     </row>
-    <row r="16" ht="31.5" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>[C3] 于每次中奖消除后提升一个倍数等级，单颗最高为 {2500X}。</t>
+          <t>[C2] 出现时即固定其倍数，之后不再改变。</t>
         </is>
       </c>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="13" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>[C3] IS UPGRADED BY ONE LEVEL AFTER EACH WINNING CASCADE, UP TO {2500X} PER SYMBOL.</t>
+          <t>[C2] KEEPS THE VALUE IT APPEARS WITH.</t>
         </is>
       </c>
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="13" t="n"/>
     </row>
-    <row r="17" ht="47.25" customHeight="1">
+    <row r="17" ht="31.5" customHeight="1">
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>该次消除后才掉落进盘面的 [C3] 不追溯升级，须等下一次中奖消除。</t>
+          <t>[C3] 于每次中奖消除后提升一个倍数等级，单颗最高为 {2500}X。</t>
         </is>
       </c>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="13" t="n"/>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>A [C3] THAT DROPS IN AFTER A CASCADE IS NOT UPGRADED FOR THAT CASCADE AND MUST WAIT FOR THE NEXT ONE.</t>
+          <t>[C3] IS UPGRADED BY ONE LEVEL AFTER EACH WINNING CASCADE, UP TO {2500}X PER SYMBOL.</t>
         </is>
       </c>
       <c r="H17" s="12" t="n"/>
       <c r="I17" s="13" t="n"/>
     </row>
-    <row r="18" ht="31.5" customHeight="1">
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
+    <row r="18" ht="47.25" customHeight="1">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>同一最终盘面出现多颗 [C2]／[C3] 时，所有倍数相加。</t>
+          <t>该次消除后才掉落进盘面的 [C3] 不追溯升级，须等下一次中奖消除。</t>
         </is>
       </c>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="13" t="n"/>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>WHEN SEVERAL [C2] / [C3] APPEAR ON THE SAME FINAL REELS, THEIR VALUES ARE ADDED TOGETHER.</t>
+          <t>A [C3] THAT DROPS IN AFTER A CASCADE IS NOT UPGRADED FOR THAT CASCADE AND MUST WAIT FOR THE NEXT ONE.</t>
         </is>
       </c>
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="13" t="n"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>副標題</t>
-        </is>
-      </c>
+    <row r="19" ht="31.5" customHeight="1">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>赔率表</t>
+          <t>同一最终盘面出现多颗 [C2]／[C3] 时，所有倍数相加。</t>
         </is>
       </c>
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="13" t="n"/>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>PAYTABLE</t>
+          <t>WHEN SEVERAL [C2] / [C3] APPEAR ON THE SAME FINAL REELS, THEIR VALUES ARE ADDED TOGETHER.</t>
         </is>
       </c>
       <c r="H19" s="12" t="n"/>
@@ -907,76 +898,68 @@
     <row r="20" ht="15.75" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>副標題</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>赔率表</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>PAYTABLE</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="13" t="n"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>賠率表</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>[M1] 12+ - 5000</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>[M2] 12+ - 2500</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>[M3] 12+ - 1500</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>[M1] 12+ - 5000</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>[M2] 12+ - 2500</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>[M3] 12+ - 1500</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>[M1] 10–11 - 2500</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>[M2] 10–11 - 1000</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>[M3] 10–11 - 500</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>[M1] 10–11 - 2500</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>[M2] 10–11 - 1000</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>[M3] 10–11 - 500</t>
         </is>
       </c>
     </row>
@@ -985,110 +968,110 @@
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>[M1] 8–9 - 1000</t>
+          <t>[M1] 10–11 - 2500</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>[M2] 8–9 - 250</t>
+          <t>[M2] 10–11 - 1000</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>[M3] 8–9 - 200</t>
+          <t>[M3] 10–11 - 500</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>[M1] 8–9 - 1000</t>
+          <t>[M1] 10–11 - 2500</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>[M2] 8–9 - 250</t>
+          <t>[M2] 10–11 - 1000</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>[M3] 8–9 - 200</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="7.95" customHeight="1">
+          <t>[M3] 10–11 - 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="10" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>[M1] 8–9 - 1000</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>[M2] 8–9 - 250</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>[M3] 8–9 - 200</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>[M1] 8–9 - 1000</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>[M2] 8–9 - 250</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>[M3] 8–9 - 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="7.95" customHeight="1">
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>[M4] 12+ - 1200</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>[A] 12+ - 1000</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>[K] 12+ - 800</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>[M4] 12+ - 1200</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>[A] 12+ - 1000</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>[K] 12+ - 800</t>
-        </is>
-      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>[M4] 10–11 - 200</t>
+          <t>[M4] 12+ - 1200</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>[A] 10–11 - 150</t>
+          <t>[A] 12+ - 1000</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>[K] 10–11 - 120</t>
+          <t>[K] 12+ - 800</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>[M4] 10–11 - 200</t>
+          <t>[M4] 12+ - 1200</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>[A] 10–11 - 150</t>
+          <t>[A] 12+ - 1000</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>[K] 10–11 - 120</t>
+          <t>[K] 12+ - 800</t>
         </is>
       </c>
     </row>
@@ -1097,382 +1080,396 @@
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>[M4] 8–9 - 150</t>
+          <t>[M4] 10–11 - 200</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>[A] 8–9 - 100</t>
+          <t>[A] 10–11 - 150</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>[K] 8–9 - 80</t>
+          <t>[K] 10–11 - 120</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>[M4] 8–9 - 150</t>
+          <t>[M4] 10–11 - 200</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>[A] 8–9 - 100</t>
+          <t>[A] 10–11 - 150</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>[K] 8–9 - 80</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="7.95" customHeight="1">
+          <t>[K] 10–11 - 120</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="10" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>[M4] 8–9 - 150</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>[A] 8–9 - 100</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>[K] 8–9 - 80</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>[M4] 8–9 - 150</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>[A] 8–9 - 100</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>[K] 8–9 - 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="7.95" customHeight="1">
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>[Q] 12+ - 500</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>[J] 12+ - 400</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>[TE] 12+ - 200</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>[Q] 12+ - 500</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>[J] 12+ - 400</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>[TE] 12+ - 200</t>
-        </is>
-      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="B29" s="10" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
+          <t>[Q] 12+ - 500</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>[J] 12+ - 400</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>[TE] 12+ - 200</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>[Q] 12+ - 500</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>[J] 12+ - 400</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>[TE] 12+ - 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
           <t>[Q] 10–11 - 100</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>[J] 10–11 - 90</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>[TE] 10–11 - 75</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>[Q] 10–11 - 100</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>[J] 10–11 - 90</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>[TE] 10–11 - 75</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="4" t="inlineStr">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>[Q] 8–9 - 50</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>[J] 8–9 - 40</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>[TE] 8–9 - 25</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>[Q] 8–9 - 50</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>[J] 8–9 - 40</t>
         </is>
       </c>
-      <c r="I30" s="4" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>[TE] 8–9 - 25</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>CASCADING FEATURE</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="13" t="n"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="13" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>连消特色</t>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="13" t="n"/>
-      <c r="G34" s="9" t="inlineStr">
-        <is>
-          <t>CASCADING FEATURE</t>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="13" t="n"/>
     </row>
-    <row r="35" ht="47.25" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>每次结算后，中奖符号会被移除，剩余符号会向下掉落并由新符号补满空位。</t>
+          <t>连消特色</t>
         </is>
       </c>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="13" t="n"/>
       <c r="G35" s="9" t="inlineStr">
         <is>
-          <t>AFTER EACH WIN EVALUATION, WINNING SYMBOLS ARE REMOVED, THE REMAINING SYMBOLS DROP DOWN, AND NEW SYMBOLS FILL THE EMPTY POSITIONS.</t>
+          <t>CASCADING FEATURE</t>
         </is>
       </c>
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="13" t="n"/>
     </row>
     <row r="36" ht="47.25" customHeight="1">
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>盘面补满后会再次结算新的中奖组合，直到不再形成新的中奖组合为止。</t>
+          <t>每次结算后，中奖符号会被移除，剩余符号会向下掉落并由新符号补满空位。</t>
         </is>
       </c>
       <c r="E36" s="12" t="n"/>
       <c r="F36" s="13" t="n"/>
       <c r="G36" s="9" t="inlineStr">
         <is>
-          <t>AFTER THE REELS ARE REFILLED, NEW WINNING COMBINATIONS ARE EVALUATED AGAIN UNTIL NO MORE WINNING COMBINATIONS ARE FORMED.</t>
+          <t>AFTER EACH WIN EVALUATION, WINNING SYMBOLS ARE REMOVED, THE REMAINING SYMBOLS DROP DOWN, AND NEW SYMBOLS FILL THE EMPTY POSITIONS.</t>
         </is>
       </c>
       <c r="H36" s="12" t="n"/>
       <c r="I36" s="13" t="n"/>
     </row>
     <row r="37" ht="47.25" customHeight="1">
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>同一次旋转所有连消的一般符号奖金先相加，再一次套用倍数。</t>
+          <t>盘面补满后会再次结算新的中奖组合，直到不再形成新的中奖组合为止。</t>
         </is>
       </c>
       <c r="E37" s="12" t="n"/>
       <c r="F37" s="13" t="n"/>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>ALL REGULAR-SYMBOL WINS FROM EVERY CASCADE OF A SPIN ARE ADDED TOGETHER FIRST, THEN THE MULTIPLIER IS APPLIED ONCE.</t>
+          <t>AFTER THE REELS ARE REFILLED, NEW WINNING COMBINATIONS ARE EVALUATED AGAIN UNTIL NO MORE WINNING COMBINATIONS ARE FORMED.</t>
         </is>
       </c>
       <c r="H37" s="12" t="n"/>
       <c r="I37" s="13" t="n"/>
     </row>
-    <row r="38"/>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+    <row r="38" ht="47.25" customHeight="1">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>同一次旋转所有连消的一般符号奖金先相加，再一次套用倍数。</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="13" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>ALL REGULAR-SYMBOL WINS FROM EVERY CASCADE OF A SPIN ARE ADDED TOGETHER FIRST, THEN THE MULTIPLIER IS APPLIED ONCE.</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="13" t="n"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>MULTIPLIER FEATURE</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="13" t="n"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
       <c r="H40" s="12" t="n"/>
       <c r="I40" s="13" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>倍数特色</t>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E41" s="12" t="n"/>
       <c r="F41" s="13" t="n"/>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>MULTIPLIER FEATURE</t>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H41" s="12" t="n"/>
       <c r="I41" s="13" t="n"/>
     </row>
-    <row r="42" ht="63" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>一般游戏中，最终盘面所有 [C2]／[C3] 的倍数总和，于所有连消结束后对该次旋转的一般符号总奖金套用一次。</t>
+          <t>倍数特色</t>
         </is>
       </c>
       <c r="E42" s="12" t="n"/>
       <c r="F42" s="13" t="n"/>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>IN THE BASE GAME, THE SUM OF ALL [C2] / [C3] VALUES ON THE FINAL REELS IS APPLIED ONCE TO THE TOTAL REGULAR-SYMBOL WIN OF THAT SPIN AFTER ALL CASCADES ARE COMPLETE.</t>
+          <t>MULTIPLIER FEATURE</t>
         </is>
       </c>
       <c r="H42" s="12" t="n"/>
       <c r="I42" s="13" t="n"/>
     </row>
-    <row r="43" ht="31.5" customHeight="1">
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
+    <row r="43" ht="63" customHeight="1">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>一般游戏的倍数只作用于该次旋转，不累积至下一次旋转。</t>
+          <t>一般游戏中，最终盘面所有 [C2]／[C3] 的倍数总和，于所有连消结束后对该次旋转的一般符号总奖金套用一次。</t>
         </is>
       </c>
       <c r="E43" s="12" t="n"/>
       <c r="F43" s="13" t="n"/>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>BASE GAME MULTIPLIERS APPLY ONLY TO THE CURRENT SPIN AND DO NOT CARRY OVER.</t>
+          <t>IN THE BASE GAME, THE SUM OF ALL [C2] / [C3] VALUES ON THE FINAL REELS IS APPLIED ONCE TO THE TOTAL REGULAR-SYMBOL WIN OF THAT SPIN AFTER ALL CASCADES ARE COMPLETE.</t>
         </is>
       </c>
       <c r="H43" s="12" t="n"/>
@@ -1483,143 +1480,142 @@
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>免费游戏的倍数会累积。</t>
+          <t>一般游戏的倍数只作用于该次旋转，不累积至下一次旋转。</t>
         </is>
       </c>
       <c r="E44" s="12" t="n"/>
       <c r="F44" s="13" t="n"/>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>IN THE FREE GAME FEATURE, THE MULTIPLIERS ACCUMULATE.</t>
+          <t>BASE GAME MULTIPLIERS APPLY ONLY TO THE CURRENT SPIN AND DO NOT CARRY OVER.</t>
         </is>
       </c>
       <c r="H44" s="12" t="n"/>
       <c r="I44" s="13" t="n"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
+    <row r="45" ht="31.5" customHeight="1">
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>乘倍效果不作用于 [C1]。</t>
+          <t>免费游戏的倍数会累积。</t>
         </is>
       </c>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="13" t="n"/>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>THE MULTIPLIER EFFECT DOES NOT APPLY TO [C1].</t>
+          <t>IN THE FREE GAME FEATURE, THE MULTIPLIERS ACCUMULATE.</t>
         </is>
       </c>
       <c r="H45" s="12" t="n"/>
       <c r="I45" s="13" t="n"/>
     </row>
-    <row r="46"/>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" s="3" t="inlineStr">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>乘倍效果不作用于 [C1]。</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="13" t="n"/>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>THE MULTIPLIER EFFECT DOES NOT APPLY TO [C1].</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n"/>
+      <c r="I46" s="13" t="n"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>FREE GAME FEATURE</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
-      <c r="H47" s="12" t="n"/>
-      <c r="I47" s="13" t="n"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="12" t="n"/>
       <c r="E48" s="12" t="n"/>
-      <c r="F48" s="13" t="n"/>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="n"/>
       <c r="H48" s="12" t="n"/>
       <c r="I48" s="13" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>免费游戏特色</t>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E49" s="12" t="n"/>
       <c r="F49" s="13" t="n"/>
-      <c r="G49" s="9" t="inlineStr">
-        <is>
-          <t>FREE GAME FEATURE</t>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H49" s="12" t="n"/>
       <c r="I49" s="13" t="n"/>
     </row>
-    <row r="50" ht="47.25" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>盘面任意位置出现 {4} 个或以上 [C1] 可触发免费游戏，获得 {15} 场免费游戏。</t>
+          <t>免费游戏特色</t>
         </is>
       </c>
       <c r="E50" s="12" t="n"/>
       <c r="F50" s="13" t="n"/>
       <c r="G50" s="9" t="inlineStr">
         <is>
-          <t>{4} OR MORE [C1] APPEARING ANYWHERE ON THE REELS WILL TRIGGER THE FREE GAME FEATURE AND AWARD {15} FREE SPINS.</t>
+          <t>FREE GAME FEATURE</t>
         </is>
       </c>
       <c r="H50" s="12" t="n"/>
       <c r="I50" s="13" t="n"/>
     </row>
-    <row r="51" ht="31.5" customHeight="1">
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
+    <row r="51" ht="47.25" customHeight="1">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>免费游戏期间再次出现 {3} 个或以上 [C1] 可触发加局，额外获得 {5} 场免费游戏。</t>
+          <t>盘面任意位置出现 {4} 个或以上 [C1] 可触发免费游戏，获得 {15} 场免费游戏。</t>
         </is>
       </c>
       <c r="E51" s="12" t="n"/>
       <c r="F51" s="13" t="n"/>
       <c r="G51" s="9" t="inlineStr">
         <is>
-          <t>DURING THE FREE GAME FEATURE, {3} OR MORE [C1] AWARD {5} ADDITIONAL FREE SPINS.</t>
+          <t>{4} OR MORE [C1] APPEARING ANYWHERE ON THE REELS WILL TRIGGER THE FREE GAME FEATURE AND AWARD {15} FREE SPINS.</t>
         </is>
       </c>
       <c r="H51" s="12" t="n"/>
@@ -1630,171 +1626,162 @@
       <c r="C52" s="10" t="n"/>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>每次免费游戏特色最多可进行 {50} 场免费游戏。</t>
+          <t>免费游戏期间再次出现 {3} 个或以上 [C1] 可触发加局，额外获得 {5} 场免费游戏。</t>
         </is>
       </c>
       <c r="E52" s="12" t="n"/>
       <c r="F52" s="13" t="n"/>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>A MAXIMUM OF {50} FREE SPINS MAY BE PLAYED DURING EACH FREE GAME FEATURE.</t>
+          <t>DURING THE FREE GAME FEATURE, {3} OR MORE [C1] AWARD {5} ADDITIONAL FREE SPINS.</t>
         </is>
       </c>
       <c r="H52" s="12" t="n"/>
       <c r="I52" s="13" t="n"/>
     </row>
-    <row r="53" ht="47.25" customHeight="1">
+    <row r="53" ht="31.5" customHeight="1">
       <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>当一次免费旋转同时有一般符号得奖、且最终盘面出现 [C2]／[C3] 时，该次盘面的倍数总和加入累积倍数。</t>
+          <t>每次免费游戏特色最多可进行 {50} 场免费游戏。</t>
         </is>
       </c>
       <c r="E53" s="12" t="n"/>
       <c r="F53" s="13" t="n"/>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>WHEN A FREE SPIN HAS BOTH A REGULAR-SYMBOL WIN AND [C2] / [C3] ON THE FINAL REELS, THE SUM OF THOSE VALUES IS ADDED TO THE ACCUMULATED MULTIPLIER.</t>
+          <t>A MAXIMUM OF {50} FREE SPINS MAY BE PLAYED DURING EACH FREE GAME FEATURE.</t>
         </is>
       </c>
       <c r="H53" s="12" t="n"/>
       <c r="I53" s="13" t="n"/>
     </row>
-    <row r="54" ht="31.5" customHeight="1">
+    <row r="54" ht="47.25" customHeight="1">
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>只有 [C1] 得奖或没有得奖的免费旋转，倍数不累积。</t>
+          <t>当一次免费旋转同时有一般符号得奖、且最终盘面出现 [C2]／[C3] 时，该次盘面的倍数总和加入累积倍数。</t>
         </is>
       </c>
       <c r="E54" s="12" t="n"/>
       <c r="F54" s="13" t="n"/>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>FREE SPINS WITH ONLY A [C1] WIN, OR WITH NO WIN, DO NOT ADD TO THE ACCUMULATED MULTIPLIER.</t>
+          <t>WHEN A FREE SPIN HAS BOTH A REGULAR-SYMBOL WIN AND [C2] / [C3] ON THE FINAL REELS, THE SUM OF THOSE VALUES IS ADDED TO THE ACCUMULATED MULTIPLIER.</t>
         </is>
       </c>
       <c r="H54" s="12" t="n"/>
       <c r="I54" s="13" t="n"/>
     </row>
-    <row r="55" ht="78.75" customHeight="1">
+    <row r="55" ht="31.5" customHeight="1">
       <c r="B55" s="10" t="n"/>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>累积倍数只在“该次最终盘面本身有 [C2]／[C3]”时作用。有一般符号得奖但盘面没有倍数符号时，该次以 {1X} 结算，累积倍数保留不归零。</t>
+          <t>只有 [C1] 得奖或没有得奖的免费旋转，倍数不累积。</t>
         </is>
       </c>
       <c r="E55" s="12" t="n"/>
       <c r="F55" s="13" t="n"/>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>THE ACCUMULATED MULTIPLIER APPLIES ONLY TO A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1X} AND THE ACCUMULATED MULTIPLIER IS KEPT, NOT RESET.</t>
+          <t>FREE SPINS WITH ONLY A [C1] WIN, OR WITH NO WIN, DO NOT ADD TO THE ACCUMULATED MULTIPLIER.</t>
         </is>
       </c>
       <c r="H55" s="12" t="n"/>
       <c r="I55" s="13" t="n"/>
     </row>
-    <row r="56" ht="47.25" customHeight="1">
+    <row r="56" ht="78.75" customHeight="1">
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>倍数在所有连消结束后，对该次免费旋转的一般符号总奖金一次套用。</t>
+          <t>累积倍数只在“该次最终盘面本身有 [C2]／[C3]”时作用。有一般符号得奖但盘面没有倍数符号时，该次以 {1}X 结算，累积倍数保留不归零。</t>
         </is>
       </c>
       <c r="E56" s="12" t="n"/>
       <c r="F56" s="13" t="n"/>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>THE MULTIPLIER IS APPLIED ONCE TO THE TOTAL REGULAR-SYMBOL WIN OF THE FREE SPIN AFTER ALL CASCADES ARE COMPLETE.</t>
+          <t>THE ACCUMULATED MULTIPLIER APPLIES ONLY TO A SPIN WHOSE OWN FINAL REELS CONTAIN [C2] / [C3]. IF A SPIN HAS A REGULAR-SYMBOL WIN BUT NO MULTIPLIER SYMBOL, IT IS PAID AT {1}X AND THE ACCUMULATED MULTIPLIER IS KEPT, NOT RESET.</t>
         </is>
       </c>
       <c r="H56" s="12" t="n"/>
       <c r="I56" s="13" t="n"/>
     </row>
-    <row r="57" ht="31.5" customHeight="1">
-      <c r="B57" s="11" t="n"/>
-      <c r="C57" s="11" t="n"/>
+    <row r="57" ht="47.25" customHeight="1">
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>累积倍数保留至整场免费游戏结束后才清除。</t>
+          <t>倍数在所有连消结束后，对该次免费旋转的一般符号总奖金一次套用。</t>
         </is>
       </c>
       <c r="E57" s="12" t="n"/>
       <c r="F57" s="13" t="n"/>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>THE ACCUMULATED MULTIPLIER IS KEPT UNTIL THE FREE GAME FEATURE ENDS.</t>
+          <t>THE MULTIPLIER IS APPLIED ONCE TO THE TOTAL REGULAR-SYMBOL WIN OF THE FREE SPIN AFTER ALL CASCADES ARE COMPLETE.</t>
         </is>
       </c>
       <c r="H57" s="12" t="n"/>
       <c r="I57" s="13" t="n"/>
     </row>
-    <row r="58"/>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="3" t="inlineStr">
+    <row r="58" ht="31.5" customHeight="1">
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>累积倍数保留至整场免费游戏结束后才清除。</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>THE ACCUMULATED MULTIPLIER IS KEPT UNTIL THE FREE GAME FEATURE ENDS.</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="13" t="n"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>EXTRA BET</t>
         </is>
       </c>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="13" t="n"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
       <c r="E60" s="12" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
       <c r="H60" s="12" t="n"/>
       <c r="I60" s="13" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>额外投注</t>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E61" s="12" t="n"/>
       <c r="F61" s="13" t="n"/>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>EXTRA BET</t>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H61" s="12" t="n"/>
@@ -1803,171 +1790,178 @@
     <row r="62" ht="15.75" customHeight="1">
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>额外投注的扣款为您所选基础投注的 {2X}。</t>
+          <t>额外投注</t>
         </is>
       </c>
       <c r="E62" s="12" t="n"/>
       <c r="F62" s="13" t="n"/>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>EXTRA BET COSTS {2X} THE BASE BET YOU SELECT.</t>
+          <t>EXTRA BET</t>
         </is>
       </c>
       <c r="H62" s="12" t="n"/>
       <c r="I62" s="13" t="n"/>
     </row>
-    <row r="63" ht="31.5" customHeight="1">
-      <c r="B63" s="10" t="n"/>
-      <c r="C63" s="10" t="n"/>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>所有奖金仍依您所选的基础投注计算。</t>
+          <t>额外投注的扣款为您所选基础投注的 {2}X。</t>
         </is>
       </c>
       <c r="E63" s="12" t="n"/>
       <c r="F63" s="13" t="n"/>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
+          <t>EXTRA BET COSTS {2}X THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H63" s="12" t="n"/>
       <c r="I63" s="13" t="n"/>
     </row>
     <row r="64" ht="31.5" customHeight="1">
-      <c r="B64" s="11" t="n"/>
-      <c r="C64" s="11" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>免费游戏的触发几率提升为一般投注的 {5} 倍。</t>
+          <t>所有奖金仍依您所选的基础投注计算。</t>
         </is>
       </c>
       <c r="E64" s="12" t="n"/>
       <c r="F64" s="13" t="n"/>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
+          <t>ALL WINS ARE STILL CALCULATED ON THE BASE BET YOU SELECT.</t>
         </is>
       </c>
       <c r="H64" s="12" t="n"/>
       <c r="I64" s="13" t="n"/>
     </row>
-    <row r="65"/>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="B66" s="3" t="inlineStr">
+    <row r="65" ht="31.5" customHeight="1">
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>免费游戏的触发几率提升为一般投注的 {5} 倍。</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="13" t="n"/>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>THE CHANCE TO TRIGGER THE FREE GAME FEATURE IS {5} TIMES THAT OF THE NORMAL BET.</t>
+        </is>
+      </c>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="13" t="n"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>BUY FEATURE</t>
         </is>
       </c>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="13" t="n"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C67" s="12" t="n"/>
+      <c r="D67" s="12" t="n"/>
       <c r="E67" s="12" t="n"/>
-      <c r="F67" s="13" t="n"/>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
       <c r="H67" s="12" t="n"/>
       <c r="I67" s="13" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>购买特色</t>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E68" s="12" t="n"/>
       <c r="F68" s="13" t="n"/>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>BUY FEATURE</t>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H68" s="12" t="n"/>
       <c r="I68" s="13" t="n"/>
     </row>
-    <row r="69" ht="31.5" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>玩家可支付 {100X} 总投注，直接购买一次免费游戏进场机会。</t>
+          <t>购买特色</t>
         </is>
       </c>
       <c r="E69" s="12" t="n"/>
       <c r="F69" s="13" t="n"/>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>BUY FEATURE CAN BE PURCHASED FOR {100X} THE TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>BUY FEATURE</t>
         </is>
       </c>
       <c r="H69" s="12" t="n"/>
       <c r="I69" s="13" t="n"/>
     </row>
     <row r="70" ht="31.5" customHeight="1">
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>完成购买后，将直接触发一次免费游戏特色。</t>
+          <t>玩家可支付 {100}X 总投注，直接购买一次免费游戏进场机会。</t>
         </is>
       </c>
       <c r="E70" s="12" t="n"/>
       <c r="F70" s="13" t="n"/>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
+          <t>BUY FEATURE CAN BE PURCHASED FOR {100}X THE TOTAL BET TO ENTER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H70" s="12" t="n"/>
@@ -1978,14 +1972,14 @@
       <c r="C71" s="10" t="n"/>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>进场盘面的 {4} 个 [C1] 依赔率表支付 {3X} 投注。</t>
+          <t>完成购买后，将直接触发一次免费游戏特色。</t>
         </is>
       </c>
       <c r="E71" s="12" t="n"/>
       <c r="F71" s="13" t="n"/>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>THE {4} [C1] ON THE ENTRY REELS PAY {3X} BET ACCORDING TO THE PAYTABLE.</t>
+          <t>COMPLETING THE PURCHASE WILL TRIGGER THE FREE GAME FEATURE DIRECTLY.</t>
         </is>
       </c>
       <c r="H71" s="12" t="n"/>
@@ -1996,179 +1990,178 @@
       <c r="C72" s="10" t="n"/>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>进入后的免费游戏规则与自然触发完全相同。</t>
+          <t>进场盘面的 {4} 个 [C1] 依赔率表支付 {3}X 投注。</t>
         </is>
       </c>
       <c r="E72" s="12" t="n"/>
       <c r="F72" s="13" t="n"/>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>ONCE ENTERED, THE FREE GAME FEATURE FOLLOWS EXACTLY THE SAME RULES AS A NATURAL TRIGGER.</t>
+          <t>THE {4} [C1] ON THE ENTRY REELS PAY {3}X BET ACCORDING TO THE PAYTABLE.</t>
         </is>
       </c>
       <c r="H72" s="12" t="n"/>
       <c r="I72" s="13" t="n"/>
     </row>
     <row r="73" ht="31.5" customHeight="1">
-      <c r="B73" s="11" t="n"/>
-      <c r="C73" s="11" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>免费游戏的奖金依您所选的基础投注计算，不依购买金额计算。</t>
+          <t>进入后的免费游戏规则与自然触发完全相同。</t>
         </is>
       </c>
       <c r="E73" s="12" t="n"/>
       <c r="F73" s="13" t="n"/>
       <c r="G73" s="9" t="inlineStr">
         <is>
-          <t>FREE GAME WINS ARE CALCULATED ON THE BASE BET YOU SELECT, NOT ON THE PURCHASE AMOUNT.</t>
+          <t>ONCE ENTERED, THE FREE GAME FEATURE FOLLOWS EXACTLY THE SAME RULES AS A NATURAL TRIGGER.</t>
         </is>
       </c>
       <c r="H73" s="12" t="n"/>
       <c r="I73" s="13" t="n"/>
     </row>
-    <row r="74"/>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="3" t="inlineStr">
+    <row r="74" ht="31.5" customHeight="1">
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>免费游戏的奖金依您所选的基础投注计算，不依购买金额计算。</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="13" t="n"/>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>FREE GAME WINS ARE CALCULATED ON THE BASE BET YOU SELECT, NOT ON THE PURCHASE AMOUNT.</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="13" t="n"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>OP JACKPOT</t>
         </is>
       </c>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
-      <c r="H75" s="12" t="n"/>
-      <c r="I75" s="13" t="n"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n"/>
       <c r="E76" s="12" t="n"/>
-      <c r="F76" s="13" t="n"/>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F76" s="12" t="n"/>
+      <c r="G76" s="12" t="n"/>
       <c r="H76" s="12" t="n"/>
       <c r="I76" s="13" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E77" s="12" t="n"/>
       <c r="F77" s="13" t="n"/>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>OP JACKPOT</t>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H77" s="12" t="n"/>
       <c r="I77" s="13" t="n"/>
     </row>
-    <row r="78" ht="31.5" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>游戏中，OP JACKPOT 特色由盘面上的 {1} 个或以上 [C1] 随机触发。</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="E78" s="12" t="n"/>
       <c r="F78" s="13" t="n"/>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>THE OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
+          <t>OP JACKPOT</t>
         </is>
       </c>
       <c r="H78" s="12" t="n"/>
       <c r="I78" s="13" t="n"/>
     </row>
-    <row r="79" ht="47.25" customHeight="1">
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="10" t="n"/>
+    <row r="79" ht="31.5" customHeight="1">
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>OP JACKPOT 特色会在画面中出现 {12} 个 [币]，其中包括 [GRAND]、[MAJOR]、[MINOR] 与 [MINI]。</t>
+          <t>游戏中，OP JACKPOT 特色由盘面上的 {1} 个或以上 [C1] 随机触发。</t>
         </is>
       </c>
       <c r="E79" s="12" t="n"/>
       <c r="F79" s="13" t="n"/>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>DURING THE OP JACKPOT FEATURE, THERE ARE {12} [COIN], WHICH CONSIST OF [GRAND], [MAJOR], [MINOR], AND [MINI].</t>
+          <t>THE OP JACKPOT FEATURE IS TRIGGERED RANDOMLY BY {1} OR MORE [C1] ON THE REELS.</t>
         </is>
       </c>
       <c r="H79" s="12" t="n"/>
       <c r="I79" s="13" t="n"/>
     </row>
-    <row r="80" ht="31.5" customHeight="1">
+    <row r="80" ht="47.25" customHeight="1">
       <c r="B80" s="10" t="n"/>
       <c r="C80" s="10" t="n"/>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>选择 {1} 个 [币] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
+          <t>OP JACKPOT 特色会在画面中出现 {12} 个 [币]，其中包括 [GRAND]、[MAJOR]、[MINOR] 与 [MINI]。</t>
         </is>
       </c>
       <c r="E80" s="12" t="n"/>
       <c r="F80" s="13" t="n"/>
       <c r="G80" s="9" t="inlineStr">
         <is>
-          <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
+          <t>DURING THE OP JACKPOT FEATURE, THERE ARE {12} [COIN], WHICH CONSIST OF [GRAND], [MAJOR], [MINOR], AND [MINI].</t>
         </is>
       </c>
       <c r="H80" s="12" t="n"/>
       <c r="I80" s="13" t="n"/>
     </row>
-    <row r="81" ht="47.25" customHeight="1">
+    <row r="81" ht="31.5" customHeight="1">
       <c r="B81" s="10" t="n"/>
       <c r="C81" s="10" t="n"/>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
+          <t>选择 {1} 个 [币] 以揭示 [GRAND]、[MAJOR]、[MINOR] 或 [MINI]。</t>
         </is>
       </c>
       <c r="E81" s="12" t="n"/>
       <c r="F81" s="13" t="n"/>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>IF THE PLAYER REVEALS {3} OF THE SAME JACKPOT SYMBOL, THE PLAYER WINS THAT JACKPOT AND IT IS ADDED TO THE TOTAL WIN.</t>
+          <t>SELECT A [COIN] TO REVEAL [GRAND], [MAJOR], [MINOR], OR [MINI].</t>
         </is>
       </c>
       <c r="H81" s="12" t="n"/>
@@ -2179,14 +2172,14 @@
       <c r="C82" s="10" t="n"/>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
+          <t>当玩家获得 {3} 个相同的 OP JACKPOT 特色符号即可获得该 OP JACKPOT 并结算总奖金。</t>
         </is>
       </c>
       <c r="E82" s="12" t="n"/>
       <c r="F82" s="13" t="n"/>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>[GRAND] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [GRAND] WILL BE UNLOCKED.</t>
+          <t>IF THE PLAYER REVEALS {3} OF THE SAME JACKPOT SYMBOL, THE PLAYER WINS THAT JACKPOT AND IT IS ADDED TO THE TOTAL WIN.</t>
         </is>
       </c>
       <c r="H82" s="12" t="n"/>
@@ -2197,32 +2190,32 @@
       <c r="C83" s="10" t="n"/>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
+          <t>[GRAND] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [GRAND]。</t>
         </is>
       </c>
       <c r="E83" s="12" t="n"/>
       <c r="F83" s="13" t="n"/>
       <c r="G83" s="9" t="inlineStr">
         <is>
-          <t>[MAJOR] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [MAJOR] WILL BE UNLOCKED.</t>
+          <t>[GRAND] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [GRAND] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H83" s="12" t="n"/>
       <c r="I83" s="13" t="n"/>
     </row>
-    <row r="84" ht="31.5" customHeight="1">
+    <row r="84" ht="47.25" customHeight="1">
       <c r="B84" s="10" t="n"/>
       <c r="C84" s="10" t="n"/>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
+          <t>[MAJOR] 为连机累进彩金。单场游戏中，投注选项选择 {2.00} 以上即可解锁 [MAJOR]。</t>
         </is>
       </c>
       <c r="E84" s="12" t="n"/>
       <c r="F84" s="13" t="n"/>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
+          <t>[MAJOR] IS A LINKED PROGRESSIVE JACKPOT. IF THE SINGLE GAME BET OPTION IS {2.00} OR ABOVE, [MAJOR] WILL BE UNLOCKED.</t>
         </is>
       </c>
       <c r="H84" s="12" t="n"/>
@@ -2233,143 +2226,142 @@
       <c r="C85" s="10" t="n"/>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>[MINI] 为红利彩金，依照投注选项改变。</t>
+          <t>[MINOR] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
       <c r="E85" s="12" t="n"/>
       <c r="F85" s="13" t="n"/>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
+          <t>[MINOR] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H85" s="12" t="n"/>
       <c r="I85" s="13" t="n"/>
     </row>
     <row r="86" ht="31.5" customHeight="1">
-      <c r="B86" s="11" t="n"/>
-      <c r="C86" s="11" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
+          <t>[MINI] 为红利彩金，依照投注选项改变。</t>
         </is>
       </c>
       <c r="E86" s="12" t="n"/>
       <c r="F86" s="13" t="n"/>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>THE HIGHER THE BET, THE HIGHER THE CHANCE TO TRIGGER THE OP JACKPOT FEATURE.</t>
+          <t>[MINI] WILL CHANGE IF THE PLAYER SELECTS A DIFFERENT BET OPTION.</t>
         </is>
       </c>
       <c r="H86" s="12" t="n"/>
       <c r="I86" s="13" t="n"/>
     </row>
-    <row r="87"/>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="B88" s="3" t="inlineStr">
+    <row r="87" ht="31.5" customHeight="1">
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>玩家投注越高触发 OP JACKPOT 特色的机会越高。</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="13" t="n"/>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>THE HIGHER THE BET, THE HIGHER THE CHANCE TO TRIGGER THE OP JACKPOT FEATURE.</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="n"/>
+      <c r="I87" s="13" t="n"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>PAY ANYWHERE</t>
         </is>
       </c>
-      <c r="C88" s="12" t="n"/>
-      <c r="D88" s="12" t="n"/>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="12" t="n"/>
-      <c r="G88" s="12" t="n"/>
-      <c r="H88" s="12" t="n"/>
-      <c r="I88" s="13" t="n"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C89" s="12" t="n"/>
+      <c r="D89" s="12" t="n"/>
       <c r="E89" s="12" t="n"/>
-      <c r="F89" s="13" t="n"/>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F89" s="12" t="n"/>
+      <c r="G89" s="12" t="n"/>
       <c r="H89" s="12" t="n"/>
       <c r="I89" s="13" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>中奖方式</t>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E90" s="12" t="n"/>
       <c r="F90" s="13" t="n"/>
-      <c r="G90" s="9" t="inlineStr">
-        <is>
-          <t>PAY ANYWHERE</t>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H90" s="12" t="n"/>
       <c r="I90" s="13" t="n"/>
     </row>
-    <row r="91" ht="47.25" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="B91" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>同一种一般符号在整个盘面合计出现 {8} 个或以上即可得奖，不要求相邻或连线。</t>
+          <t>中奖方式</t>
         </is>
       </c>
       <c r="E91" s="12" t="n"/>
       <c r="F91" s="13" t="n"/>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>{8} OR MORE OF THE SAME REGULAR SYMBOL ANYWHERE ON THE GRID FORM A WIN. THEY DO NOT NEED TO BE ADJACENT OR ON A LINE.</t>
+          <t>PAY ANYWHERE</t>
         </is>
       </c>
       <c r="H91" s="12" t="n"/>
       <c r="I91" s="13" t="n"/>
     </row>
-    <row r="92" ht="31.5" customHeight="1">
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
+    <row r="92" ht="47.25" customHeight="1">
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>同一盘面可有多种一般符号同时得奖，各自支付一次。</t>
+          <t>同一种一般符号在整个盘面合计出现 {8} 个或以上即可得奖，不要求相邻或连线。</t>
         </is>
       </c>
       <c r="E92" s="12" t="n"/>
       <c r="F92" s="13" t="n"/>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>SEVERAL REGULAR SYMBOL TYPES MAY WIN ON THE SAME GRID AND EACH IS PAID ONCE.</t>
+          <t>{8} OR MORE OF THE SAME REGULAR SYMBOL ANYWHERE ON THE GRID FORM A WIN. THEY DO NOT NEED TO BE ADJACENT OR ON A LINE.</t>
         </is>
       </c>
       <c r="H92" s="12" t="n"/>
@@ -2380,99 +2372,90 @@
       <c r="C93" s="10" t="n"/>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>一般符号奖金依赔率表倍数乘以投注计算。</t>
+          <t>同一盘面可有多种一般符号同时得奖，各自支付一次。</t>
         </is>
       </c>
       <c r="E93" s="12" t="n"/>
       <c r="F93" s="13" t="n"/>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>A REGULAR SYMBOL WIN IS PAID AT THE PAYTABLE MULTIPLIER OF THE BET.</t>
+          <t>SEVERAL REGULAR SYMBOL TYPES MAY WIN ON THE SAME GRID AND EACH IS PAID ONCE.</t>
         </is>
       </c>
       <c r="H93" s="12" t="n"/>
       <c r="I93" s="13" t="n"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="B94" s="11" t="n"/>
-      <c r="C94" s="11" t="n"/>
+    <row r="94" ht="31.5" customHeight="1">
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>本游戏没有百搭符号。</t>
+          <t>一般符号奖金依赔率表倍数乘以投注计算。</t>
         </is>
       </c>
       <c r="E94" s="12" t="n"/>
       <c r="F94" s="13" t="n"/>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>THIS GAME HAS NO WILD SYMBOL.</t>
+          <t>A REGULAR SYMBOL WIN IS PAID AT THE PAYTABLE MULTIPLIER OF THE BET.</t>
         </is>
       </c>
       <c r="H94" s="12" t="n"/>
       <c r="I94" s="13" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="B96" s="3" t="inlineStr">
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>本游戏没有百搭符号。</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="13" t="n"/>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>THIS GAME HAS NO WILD SYMBOL.</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="13" t="n"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>GAME RULE</t>
         </is>
       </c>
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="12" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="12" t="n"/>
-      <c r="H96" s="12" t="n"/>
-      <c r="I96" s="13" t="n"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>簡中</t>
-        </is>
-      </c>
+      <c r="C97" s="12" t="n"/>
+      <c r="D97" s="12" t="n"/>
       <c r="E97" s="12" t="n"/>
-      <c r="F97" s="13" t="n"/>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>英文</t>
-        </is>
-      </c>
+      <c r="F97" s="12" t="n"/>
+      <c r="G97" s="12" t="n"/>
       <c r="H97" s="12" t="n"/>
       <c r="I97" s="13" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>主要標題</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>游戏规则</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>簡中</t>
         </is>
       </c>
       <c r="E98" s="12" t="n"/>
       <c r="F98" s="13" t="n"/>
-      <c r="G98" s="9" t="inlineStr">
-        <is>
-          <t>GAME RULES</t>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>英文</t>
         </is>
       </c>
       <c r="H98" s="12" t="n"/>
@@ -2481,258 +2464,284 @@
     <row r="99" ht="15.75" customHeight="1">
       <c r="B99" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>規則說明</t>
+          <t>主要標題</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>选择您想要玩的投注选项。</t>
+          <t>游戏规则</t>
         </is>
       </c>
       <c r="E99" s="12" t="n"/>
       <c r="F99" s="13" t="n"/>
       <c r="G99" s="9" t="inlineStr">
         <is>
-          <t>SELECT THE BET OPTION YOU WISH TO PLAY.</t>
+          <t>GAME RULES</t>
         </is>
       </c>
       <c r="H99" s="12" t="n"/>
       <c r="I99" s="13" t="n"/>
     </row>
-    <row r="100" ht="31.5" customHeight="1">
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>規則說明</t>
+        </is>
+      </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>所有中奖金额均乘以投注选项，除非是累积奖。</t>
+          <t>选择您想要玩的投注选项。</t>
         </is>
       </c>
       <c r="E100" s="12" t="n"/>
       <c r="F100" s="13" t="n"/>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>ALL WINS ARE MULTIPLIED BY THE BET OPTION EXCEPT PROGRESSIVE BONUSES.</t>
+          <t>SELECT THE BET OPTION YOU WISH TO PLAY.</t>
         </is>
       </c>
       <c r="H100" s="12" t="n"/>
       <c r="I100" s="13" t="n"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="31.5" customHeight="1">
       <c r="B101" s="10" t="n"/>
       <c r="C101" s="10" t="n"/>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>游戏出现故障时，所有赔付与游戏结果均视为无效。</t>
+          <t>所有中奖金额均乘以投注选项，除非是累积奖。</t>
         </is>
       </c>
       <c r="E101" s="12" t="n"/>
       <c r="F101" s="13" t="n"/>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
+          <t>ALL WINS ARE MULTIPLIED BY THE BET OPTION EXCEPT PROGRESSIVE BONUSES.</t>
         </is>
       </c>
       <c r="H101" s="12" t="n"/>
       <c r="I101" s="13" t="n"/>
     </row>
-    <row r="102" ht="63" customHeight="1">
-      <c r="B102" s="11" t="n"/>
-      <c r="C102" s="11" t="n"/>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="10" t="n"/>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>若玩家在免费游戏期间中断连接，系统将自动完成该局结算，并将中奖金额加入余额。</t>
+          <t>游戏出现故障时，所有赔付与游戏结果均视为无效。</t>
         </is>
       </c>
       <c r="E102" s="12" t="n"/>
       <c r="F102" s="13" t="n"/>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL CALCULATE THE GAME RESULTS AUTOMATICALLY AND THE WINNING PRIZES WILL BE ADDED INTO THE BALANCE.</t>
+          <t>MALFUNCTION VOIDS ALL PAYS AND PLAYS.</t>
         </is>
       </c>
       <c r="H102" s="12" t="n"/>
       <c r="I102" s="13" t="n"/>
     </row>
-    <row r="103"/>
-    <row r="104"/>
+    <row r="103" ht="63" customHeight="1">
+      <c r="B103" s="11" t="n"/>
+      <c r="C103" s="11" t="n"/>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>若玩家在免费游戏期间中断连接，系统将自动完成该局结算，并将中奖金额加入余额。</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="13" t="n"/>
+      <c r="G103" s="9" t="inlineStr">
+        <is>
+          <t>IF THE PLAYER LOSES CONNECTION DURING THE FREE GAME FEATURE, THE SYSTEM WILL CALCULATE THE GAME RESULTS AUTOMATICALLY AND THE WINNING PRIZES WILL BE ADDED INTO THE BALANCE.</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="n"/>
+      <c r="I103" s="13" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="175">
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="G103:I103"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="B51:B58"/>
     <mergeCell ref="G13:I13"/>
     <mergeCell ref="G62:I62"/>
+    <mergeCell ref="G87:I87"/>
+    <mergeCell ref="C92:C95"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="B50:B57"/>
+    <mergeCell ref="C14:C19"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="B96:I96"/>
-    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C70:C74"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="B48:I48"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D102:F102"/>
+    <mergeCell ref="G65:I65"/>
     <mergeCell ref="G79:I79"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="G73:I73"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D92:F92"/>
     <mergeCell ref="G63:I63"/>
-    <mergeCell ref="B88:I88"/>
     <mergeCell ref="G16:I16"/>
-    <mergeCell ref="B62:B64"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="G50:I50"/>
     <mergeCell ref="G90:I90"/>
-    <mergeCell ref="C78:C86"/>
     <mergeCell ref="D94:F94"/>
-    <mergeCell ref="C91:C94"/>
     <mergeCell ref="G9:I9"/>
+    <mergeCell ref="C51:C58"/>
+    <mergeCell ref="C63:C65"/>
     <mergeCell ref="G52:I52"/>
-    <mergeCell ref="C35:C37"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="G42:I42"/>
+    <mergeCell ref="C79:C87"/>
     <mergeCell ref="D80:F80"/>
     <mergeCell ref="B5:I5"/>
+    <mergeCell ref="B76:I76"/>
+    <mergeCell ref="B70:B74"/>
+    <mergeCell ref="C36:C38"/>
     <mergeCell ref="D57:F57"/>
     <mergeCell ref="G101:I101"/>
-    <mergeCell ref="B75:I75"/>
     <mergeCell ref="G6:I6"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B47:I47"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="C42:C45"/>
     <mergeCell ref="G69:I69"/>
-    <mergeCell ref="B59:I59"/>
     <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B78:B86"/>
     <mergeCell ref="G78:I78"/>
+    <mergeCell ref="D91:F91"/>
     <mergeCell ref="G92:I92"/>
-    <mergeCell ref="D91:F91"/>
     <mergeCell ref="D43:F43"/>
-    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B43:B46"/>
     <mergeCell ref="G14:I14"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B39:I39"/>
     <mergeCell ref="G80:I80"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="G55:I55"/>
     <mergeCell ref="G64:I64"/>
+    <mergeCell ref="D74:F74"/>
     <mergeCell ref="D68:F68"/>
-    <mergeCell ref="C62:C64"/>
     <mergeCell ref="D83:F83"/>
     <mergeCell ref="G51:I51"/>
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="G54:I54"/>
-    <mergeCell ref="D67:F67"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="G41:I41"/>
     <mergeCell ref="D85:F85"/>
     <mergeCell ref="D54:F54"/>
+    <mergeCell ref="B92:B95"/>
     <mergeCell ref="G81:I81"/>
-    <mergeCell ref="C14:C18"/>
     <mergeCell ref="G56:I56"/>
-    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D69:F69"/>
     <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D69:F69"/>
     <mergeCell ref="G43:I43"/>
     <mergeCell ref="G71:I71"/>
-    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="B33:I33"/>
     <mergeCell ref="G98:I98"/>
-    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D46:F46"/>
     <mergeCell ref="G8:I8"/>
-    <mergeCell ref="C20:C30"/>
     <mergeCell ref="G17:I17"/>
     <mergeCell ref="D86:F86"/>
     <mergeCell ref="G82:I82"/>
+    <mergeCell ref="D95:F95"/>
     <mergeCell ref="G10:I10"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="G53:I53"/>
     <mergeCell ref="G93:I93"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="B66:I66"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G74:I74"/>
     <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G68:I68"/>
     <mergeCell ref="D78:F78"/>
-    <mergeCell ref="G34:I34"/>
     <mergeCell ref="G83:I83"/>
     <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="G58:I58"/>
     <mergeCell ref="C9:C12"/>
+    <mergeCell ref="C100:C103"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="G45:I45"/>
-    <mergeCell ref="C69:C73"/>
+    <mergeCell ref="D58:F58"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="A1:I2"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="B67:I67"/>
     <mergeCell ref="D8:F8"/>
     <mergeCell ref="G100:I100"/>
-    <mergeCell ref="C50:C57"/>
-    <mergeCell ref="D33:F33"/>
     <mergeCell ref="D73:F73"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="D51:F51"/>
     <mergeCell ref="D42:F42"/>
-    <mergeCell ref="G94:I94"/>
     <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="B79:B87"/>
     <mergeCell ref="G84:I84"/>
     <mergeCell ref="G44:I44"/>
+    <mergeCell ref="G46:I46"/>
     <mergeCell ref="G102:I102"/>
-    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="D44:F44"/>
     <mergeCell ref="G12:I12"/>
-    <mergeCell ref="D44:F44"/>
     <mergeCell ref="G72:I72"/>
+    <mergeCell ref="D20:F20"/>
     <mergeCell ref="G86:I86"/>
     <mergeCell ref="D34:F34"/>
+    <mergeCell ref="B40:I40"/>
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="G70:I70"/>
     <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B89:I89"/>
     <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="B100:B103"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D6:F6"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="B32:I32"/>
     <mergeCell ref="D77:F77"/>
+    <mergeCell ref="B97:I97"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="G57:I57"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="D70:F70"/>
+    <mergeCell ref="G49:I49"/>
     <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G49:I49"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="D103:F103"/>
     <mergeCell ref="D72:F72"/>
+    <mergeCell ref="C21:C31"/>
     <mergeCell ref="D62:F62"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="B14:B19"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G76:I76"/>
     <mergeCell ref="G91:I91"/>
     <mergeCell ref="G85:I85"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D98:F98"/>
     <mergeCell ref="G99:I99"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="C99:C102"/>
-    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="C43:C46"/>
     <mergeCell ref="D79:F79"/>
-    <mergeCell ref="B20:B30"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G77:I77"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G77:I77"/>
     <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D63:F63"/>
     <mergeCell ref="D19:F19"/>
     <mergeCell ref="D90:F90"/>
-    <mergeCell ref="G67:I67"/>
+    <mergeCell ref="D65:F65"/>
     <mergeCell ref="G61:I61"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="B91:B94"/>
+    <mergeCell ref="B21:B31"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D49:F49"/>
   </mergeCells>
